--- a/amostras/principal/P08/matriz_rastreabilidade_P08.xlsx
+++ b/amostras/principal/P08/matriz_rastreabilidade_P08.xlsx
@@ -801,28 +801,28 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Não Aplicável</t>
+          <t>Nenhuma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Não Aplicável</t>
+          <t>Nenhum</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Amostra Não Preenchida</t>
+          <t>Nenhuma / Sem Achados</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Não Aplicável</t>
+          <t>Nenhuma</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Aguardando geração (Passo 1 pendente)</t>
+          <t>Não se aplica (amostra limpa)</t>
         </is>
       </c>
     </row>
